--- a/data/Lead_information_Formulario_Brasil_Main.xlsx
+++ b/data/Lead_information_Formulario_Brasil_Main.xlsx
@@ -1,126 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elian Trabajo\Documents\Ocioso_Update\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Formulario</t>
+  </si>
+  <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t>Documento</t>
+  </si>
+  <si>
+    <t>Celular</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Región</t>
+  </si>
+  <si>
+    <t>Ciudad</t>
+  </si>
+  <si>
+    <t>Concesionario</t>
+  </si>
+  <si>
+    <t>Fecha estimada</t>
+  </si>
+  <si>
+    <t>chasis</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.br/servicos/blindagem</t>
+  </si>
+  <si>
+    <t>https://secure-developments.com/commonwealth/brasil/gm_forms/blindagem</t>
+  </si>
+  <si>
+    <t>Paula</t>
+  </si>
+  <si>
+    <t>García Gutierrez</t>
+  </si>
+  <si>
+    <t>64334540031</t>
+  </si>
+  <si>
+    <t>38946408700</t>
+  </si>
+  <si>
+    <t>paulagarciagutierrez.br83@mrm.com</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -129,10 +122,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -262,6 +255,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -285,10 +279,11 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -297,13 +292,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -379,6 +374,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -398,129 +394,93 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Formulario</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Apellido</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Celular</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Región</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Ciudad</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Concesionario</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Fecha estimada</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>chasis</t>
-        </is>
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://secure-developments.com/commonwealth/brasil/gm_forms/sos-electricos-equinox-ev?model=equinox%20EV</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Monica Luis</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Silva</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>45278778016</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>45914962985</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>monicaluissilva.br80@mrm.com</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4"/>
+    </row>
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Lead_information_Formulario_Brasil_Main.xlsx
+++ b/data/Lead_information_Formulario_Brasil_Main.xlsx
@@ -1,119 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elian Trabajo\Documents\Ocioso_Update\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>Formulario</t>
-  </si>
-  <si>
-    <t>Modelo</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Apellido</t>
-  </si>
-  <si>
-    <t>Documento</t>
-  </si>
-  <si>
-    <t>Celular</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Región</t>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>Concesionario</t>
-  </si>
-  <si>
-    <t>Fecha estimada</t>
-  </si>
-  <si>
-    <t>chasis</t>
-  </si>
-  <si>
-    <t>https://www.chevrolet.com.br/servicos/blindagem</t>
-  </si>
-  <si>
-    <t>https://secure-developments.com/commonwealth/brasil/gm_forms/blindagem</t>
-  </si>
-  <si>
-    <t>Paula</t>
-  </si>
-  <si>
-    <t>García Gutierrez</t>
-  </si>
-  <si>
-    <t>64334540031</t>
-  </si>
-  <si>
-    <t>38946408700</t>
-  </si>
-  <si>
-    <t>paulagarciagutierrez.br83@mrm.com</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -122,10 +129,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -255,7 +262,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -279,11 +285,10 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -292,13 +297,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -374,7 +379,6 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -394,93 +398,262 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Formulario</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Apellido</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Celular</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Región</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Ciudad</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Concesionario</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Fecha estimada</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>chasis</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.chevrolet.com.br/chevrolet-sempre/form</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://secure-developments.com/commonwealth/brasil/gm_forms/breca-varejo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Andrés</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Valdez</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60557355044</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>85936904034</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>andresvaldez.br36@mrm.com</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.chevrolet.com.br/eletrico/para-voce/clube-myev</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://secure-developments.com/commonwealth/brasil/gm_forms/clubemyev</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cristian Fernanda</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Gutierrez Fuentes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>87545377036</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12918728524</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>cristianfernandagutierrezfuentes.br49@mrm.com</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4"/>
-      <c r="B4"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.chevrolet.com.br/comprar-carro-equinox-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://secure-developments.com/commonwealth/brasil/gm_forms/vehicle-shopper-sin-stock?model=equinox</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Paola Pablo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ibáñez Guerrero</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>76689203077</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>63995850422</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>paolapabloibanezguerrero.br53@mrm.com</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5"/>
-      <c r="B5"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.chevrolet.com.br/solicitar-contato</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://secure-developments.com/commonwealth/brasil/gm_forms/raq</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rodrigo Ana</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Rojas</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>89871262000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>41918279426</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rodrigoanarojas.br75@mrm.com</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
